--- a/ex.xlsx
+++ b/ex.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D2">
@@ -445,12 +445,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2018-01-17 8:32</t>
+          <t>2018-01-17T8:32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2018-01-17 11:28</t>
+          <t>2018-01-17T11:28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D3">
@@ -493,12 +493,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2018-01-24 9:44</t>
+          <t>2018-01-24T9:44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2018-01-24 12:40</t>
+          <t>2018-01-24T12:40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D4">
@@ -541,12 +541,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2018-01-31 8:12</t>
+          <t>2018-01-31T8:12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2018-01-31 11:18</t>
+          <t>2018-01-31T11:18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D5">
@@ -589,12 +589,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2018-02-07 9:43</t>
+          <t>2018-02-07T9:43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2018-02-07 12:39</t>
+          <t>2018-02-07T12:39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D6">
@@ -637,12 +637,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2018-02-14 9:51</t>
+          <t>2018-02-14T9:51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2018-02-14 12:47</t>
+          <t>2018-02-14T12:47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D7">
@@ -685,12 +685,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2018-02-21 8:19</t>
+          <t>2018-02-21T8:19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2018-02-21 11:15</t>
+          <t>2018-02-21T11:15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D8">
@@ -733,12 +733,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2018-02-28 8:42</t>
+          <t>2018-02-28T8:42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2018-02-28 11:38</t>
+          <t>2018-02-28T11:38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D9">
@@ -773,12 +773,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2018-03-07 NA</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2018-03-07 NA</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D10">
@@ -821,12 +821,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2018-03-14 10:13</t>
+          <t>2018-03-14T10:13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2018-03-14 13:19</t>
+          <t>2018-03-14T13:19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D11">
@@ -869,12 +869,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2018-03-21 9:50</t>
+          <t>2018-03-21T9:50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2018-03-21 12:46</t>
+          <t>2018-03-21T12:46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02092</t>
+          <t>PEAR14091511-BRZ02-02092</t>
         </is>
       </c>
       <c r="D12">
@@ -917,12 +917,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2018-03-28 8:16</t>
+          <t>2018-03-28T8:16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2018-03-28 11:12</t>
+          <t>2018-03-28T11:12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D13">
@@ -965,12 +965,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2018-01-18 11:33</t>
+          <t>2018-01-18T11:33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2018-01-18 14:29</t>
+          <t>2018-01-18T14:29</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D14">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2018-01-25 11:50</t>
+          <t>2018-01-25T11:50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2018-01-25 14:46</t>
+          <t>2018-01-25T14:46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D15">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2018-02-01 9:48</t>
+          <t>2018-02-01T9:48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2018-02-01 12:44</t>
+          <t>2018-02-01T12:44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D16">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2018-02-08 8:46</t>
+          <t>2018-02-08T8:46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2018-02-08 11:42</t>
+          <t>2018-02-08T11:42</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D17">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2018-02-15 8:49</t>
+          <t>2018-02-15T8:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2018-02-15 11:45</t>
+          <t>2018-02-15T11:45</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PEAR1409151102-02103</t>
+          <t>PEAR14091511-BRZ02-02103</t>
         </is>
       </c>
       <c r="D18">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2018-02-22 8:41</t>
+          <t>2018-02-22T8:41</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2018-02-22 11:37</t>
+          <t>2018-02-22T11:37</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D19">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2018-01-19 8:11</t>
+          <t>2018-01-19T8:11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2018-01-19 11:17</t>
+          <t>2018-01-19T11:17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D20">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2018-01-26 8:30</t>
+          <t>2018-01-26T8:30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2018-01-26 11:26</t>
+          <t>2018-01-26T11:26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D21">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2018-02-02 9:22</t>
+          <t>2018-02-02T9:22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2018-02-02 12:18</t>
+          <t>2018-02-02T12:18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D22">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2018-02-09 9:34</t>
+          <t>2018-02-09T9:34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2018-02-09 12:30</t>
+          <t>2018-02-09T12:30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D23">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2018-02-16 8:35</t>
+          <t>2018-02-16T8:35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2018-02-16 11:31</t>
+          <t>2018-02-16T11:31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D24">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2018-02-23 11:17</t>
+          <t>2018-02-23T11:17</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2018-02-23 14:13</t>
+          <t>2018-02-23T14:13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D25">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2018-03-02 9:43</t>
+          <t>2018-03-02T9:43</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2018-03-02 12:39</t>
+          <t>2018-03-02T12:39</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D26">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2018-03-09 11:25</t>
+          <t>2018-03-09T11:25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2018-03-09 14:21</t>
+          <t>2018-03-09T14:21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PEAR1409151103-05662</t>
+          <t>PEAR14091511-BRZ03-05662</t>
         </is>
       </c>
       <c r="D27">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2018-03-16 8:55</t>
+          <t>2018-03-16T8:55</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2018-03-16 11:51</t>
+          <t>2018-03-16T11:51</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D28">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2018-01-07 8:10</t>
+          <t>2018-01-07T8:10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2018-01-07 11:16</t>
+          <t>2018-01-07T11:16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D29">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2018-01-14 8:19</t>
+          <t>2018-01-14T8:19</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2018-01-14 11:15</t>
+          <t>2018-01-14T11:15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D30">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2018-01-21 8:29</t>
+          <t>2018-01-21T8:29</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2018-01-21 11:25</t>
+          <t>2018-01-21T11:25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D31">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2018-01-28 NA</t>
+          <t>2018-01-28</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2018-01-28 NA</t>
+          <t>2018-01-28</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D32">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2018-02-04 11:47</t>
+          <t>2018-02-04T11:47</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2018-02-04 14:43</t>
+          <t>2018-02-04T14:43</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D33">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2018-02-11 11:13</t>
+          <t>2018-02-11T11:13</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2018-02-11 14:19</t>
+          <t>2018-02-11T14:19</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D34">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2018-02-18 10:35</t>
+          <t>2018-02-18T10:35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2018-02-18 13:31</t>
+          <t>2018-02-18T13:31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D35">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2018-02-25 9:31</t>
+          <t>2018-02-25T9:31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2018-02-25 12:27</t>
+          <t>2018-02-25T12:27</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D36">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2018-03-04 8:17</t>
+          <t>2018-03-04T8:17</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2018-03-04 11:13</t>
+          <t>2018-03-04T11:13</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D37">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2018-03-11 8:29</t>
+          <t>2018-03-11T8:29</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2018-03-11 11:25</t>
+          <t>2018-03-11T11:25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D38">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2018-03-18 8:19</t>
+          <t>2018-03-18T8:19</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2018-03-18 11:15</t>
+          <t>2018-03-18T11:15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PEAR1409151102-01002</t>
+          <t>PEAR14091511-CAN02-01002</t>
         </is>
       </c>
       <c r="D39">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2018-03-25 8:00</t>
+          <t>2018-03-25T8:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2018-03-25 11:11</t>
+          <t>2018-03-25T11:11</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D40">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2018-01-08 9:11</t>
+          <t>2018-01-08T9:11</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2018-01-08 12:13</t>
+          <t>2018-01-08T12:13</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D41">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2018-01-15 11:11</t>
+          <t>2018-01-15T11:11</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2018-01-15 14:13</t>
+          <t>2018-01-15T14:13</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D42">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2018-01-22 8:48</t>
+          <t>2018-01-22T8:48</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2018-01-22 11:44</t>
+          <t>2018-01-22T11:44</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D43">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2018-01-29 8:18</t>
+          <t>2018-01-29T8:18</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2018-01-29 11:14</t>
+          <t>2018-01-29T11:14</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D44">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2018-02-05 8:16</t>
+          <t>2018-02-05T8:16</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2018-02-05 11:12</t>
+          <t>2018-02-05T11:12</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D45">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2018-02-12 8:30</t>
+          <t>2018-02-12T8:30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2018-02-12 11:26</t>
+          <t>2018-02-12T11:26</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PEAR1409151107-01001</t>
+          <t>PEAR14091511-CAN07-01001</t>
         </is>
       </c>
       <c r="D46">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2018-02-19 8:32</t>
+          <t>2018-02-19T8:32</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2018-02-19 11:28</t>
+          <t>2018-02-19T11:28</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01002</t>
+          <t>PEAR14091511-CAN09-01002</t>
         </is>
       </c>
       <c r="D47">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2018-01-09 8:33</t>
+          <t>2018-01-09T8:33</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2018-01-09 11:29</t>
+          <t>2018-01-09T11:29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01002</t>
+          <t>PEAR14091511-CAN09-01002</t>
         </is>
       </c>
       <c r="D48">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2018-01-16 9:12</t>
+          <t>2018-01-16T9:12</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2018-01-16 12:12</t>
+          <t>2018-01-16T12:12</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01002</t>
+          <t>PEAR14091511-CAN09-01002</t>
         </is>
       </c>
       <c r="D49">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2018-01-23 9:38</t>
+          <t>2018-01-23T9:38</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2018-01-23 12:34</t>
+          <t>2018-01-23T12:34</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01002</t>
+          <t>PEAR14091511-CAN09-01002</t>
         </is>
       </c>
       <c r="D50">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2018-01-30 9:37</t>
+          <t>2018-01-30T9:37</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2018-01-30 12:33</t>
+          <t>2018-01-30T12:33</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01002</t>
+          <t>PEAR14091511-CAN09-01002</t>
         </is>
       </c>
       <c r="D51">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2018-02-06 9:39</t>
+          <t>2018-02-06T9:39</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2018-02-06 12:35</t>
+          <t>2018-02-06T12:35</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D52">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2018-01-26 9:58</t>
+          <t>2018-01-26T9:58</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2018-01-26 12:54</t>
+          <t>2018-01-26T12:54</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D53">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2018-02-02 9:49</t>
+          <t>2018-02-02T9:49</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2018-02-02 12:45</t>
+          <t>2018-02-02T12:45</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D54">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2018-02-09 9:46</t>
+          <t>2018-02-09T9:46</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2018-02-09 12:42</t>
+          <t>2018-02-09T12:42</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D55">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2018-02-16 9:22</t>
+          <t>2018-02-16T9:22</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2018-02-16 12:18</t>
+          <t>2018-02-16T12:18</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D56">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2018-02-23 9:18</t>
+          <t>2018-02-23T9:18</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2018-02-23 12:14</t>
+          <t>2018-02-23T12:14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D57">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2018-03-02 8:56</t>
+          <t>2018-03-02T8:56</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2018-03-02 11:52</t>
+          <t>2018-03-02T11:52</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PEAR1409151105-90231</t>
+          <t>PEAR14091511-CHA05-90231</t>
         </is>
       </c>
       <c r="D58">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2018-03-09 8:17</t>
+          <t>2018-03-09T8:17</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2018-03-09 11:13</t>
+          <t>2018-03-09T11:13</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D59">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2018-01-24 8:28</t>
+          <t>2018-01-24T8:28</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2018-01-24 11:24</t>
+          <t>2018-01-24T11:24</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D60">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2018-01-31 8:27</t>
+          <t>2018-01-31T8:27</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2018-01-31 11:23</t>
+          <t>2018-01-31T11:23</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D61">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2018-02-07 8:27</t>
+          <t>2018-02-07T8:27</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2018-02-07 11:23</t>
+          <t>2018-02-07T11:23</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D62">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2018-02-14 8:53</t>
+          <t>2018-02-14T8:53</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2018-02-14 11:49</t>
+          <t>2018-02-14T11:49</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D63">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2018-02-21 8:59</t>
+          <t>2018-02-21T8:59</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2018-02-21 11:55</t>
+          <t>2018-02-21T11:55</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D64">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2018-02-28 8:53</t>
+          <t>2018-02-28T8:53</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2018-02-28 11:49</t>
+          <t>2018-02-28T11:49</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PEAR1409151107-90630</t>
+          <t>PEAR14091511-CRO07-90630</t>
         </is>
       </c>
       <c r="D65">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2018-03-07 8:18</t>
+          <t>2018-03-07T8:18</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2018-03-07 11:14</t>
+          <t>2018-03-07T11:14</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D66">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2018-01-27 8:44</t>
+          <t>2018-01-27T8:44</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2018-01-27 11:40</t>
+          <t>2018-01-27T11:40</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D67">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2018-02-03 8:51</t>
+          <t>2018-02-03T8:51</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2018-02-03 11:47</t>
+          <t>2018-02-03T11:47</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D68">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2018-02-10 8:14</t>
+          <t>2018-02-10T8:14</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2018-02-10 11:10</t>
+          <t>2018-02-10T11:10</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D69">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2018-02-17 8:16</t>
+          <t>2018-02-17T8:16</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2018-02-17 11:12</t>
+          <t>2018-02-17T11:12</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D70">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2018-02-24 8:21</t>
+          <t>2018-02-24T8:21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2018-02-24 11:17</t>
+          <t>2018-02-24T11:17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D71">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2018-03-03 8:20</t>
+          <t>2018-03-03T8:20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2018-03-03 11:16</t>
+          <t>2018-03-03T11:16</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D72">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2018-03-10 8:33</t>
+          <t>2018-03-10T8:33</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2018-03-10 11:29</t>
+          <t>2018-03-10T11:29</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01021</t>
+          <t>PEAR14091511-CZE01-01021</t>
         </is>
       </c>
       <c r="D73">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2018-03-17 8:14</t>
+          <t>2018-03-17T8:14</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2018-03-17 11:10</t>
+          <t>2018-03-17T11:10</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D74">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2018-01-21 9:38</t>
+          <t>2018-01-21T9:38</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2018-01-21 12:34</t>
+          <t>2018-01-21T12:34</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D75">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2018-01-28 9:56</t>
+          <t>2018-01-28T9:56</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2018-01-28 12:52</t>
+          <t>2018-01-28T12:52</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D76">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2018-02-04 9:19</t>
+          <t>2018-02-04T9:19</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2018-02-04 12:15</t>
+          <t>2018-02-04T12:15</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D77">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2018-02-11 10:50</t>
+          <t>2018-02-11T10:50</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2018-02-11 13:46</t>
+          <t>2018-02-11T13:46</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D78">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2018-02-18 10:42</t>
+          <t>2018-02-18T10:42</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2018-02-18 13:38</t>
+          <t>2018-02-18T13:38</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D79">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2018-02-25 10:38</t>
+          <t>2018-02-25T10:38</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2018-02-25 13:34</t>
+          <t>2018-02-25T13:34</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PEAR1409151101-01011</t>
+          <t>PEAR14091511-DAN01-01011</t>
         </is>
       </c>
       <c r="D80">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2018-03-04 10:46</t>
+          <t>2018-03-04T10:46</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2018-03-04 13:42</t>
+          <t>2018-03-04T13:42</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D81">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2018-01-28 10:27</t>
+          <t>2018-01-28T10:27</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2018-01-28 13:23</t>
+          <t>2018-01-28T13:23</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D82">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2018-02-04 10:46</t>
+          <t>2018-02-04T10:46</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2018-02-04 13:42</t>
+          <t>2018-02-04T13:42</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D83">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2018-02-11 8:40</t>
+          <t>2018-02-11T8:40</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2018-02-11 11:36</t>
+          <t>2018-02-11T11:36</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D84">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2018-02-18 8:49</t>
+          <t>2018-02-18T8:49</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2018-02-18 11:45</t>
+          <t>2018-02-18T11:45</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D85">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2018-02-25 8:27</t>
+          <t>2018-02-25T8:27</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2018-02-25 11:23</t>
+          <t>2018-02-25T11:23</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D86">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2018-03-04 8:24</t>
+          <t>2018-03-04T8:24</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2018-03-04 11:20</t>
+          <t>2018-03-04T11:20</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PEAR1409151103-01002</t>
+          <t>PEAR14091511-ESP03-01002</t>
         </is>
       </c>
       <c r="D87">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2018-03-11 8:52</t>
+          <t>2018-03-11T8:52</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2018-03-11 11:48</t>
+          <t>2018-03-11T11:48</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D88">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2018-01-10 8:30</t>
+          <t>2018-01-10T8:30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2018-01-10 11:26</t>
+          <t>2018-01-10T11:26</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D89">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2018-01-17 8:32</t>
+          <t>2018-01-17T8:32</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2018-01-17 11:28</t>
+          <t>2018-01-17T11:28</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D90">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2018-01-24 8:43</t>
+          <t>2018-01-24T8:43</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2018-01-24 11:39</t>
+          <t>2018-01-24T11:39</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D91">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2018-01-31 NA</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2018-01-31 NA</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D92">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2018-02-07 8:53</t>
+          <t>2018-02-07T8:53</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2018-02-07 11:49</t>
+          <t>2018-02-07T11:49</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D93">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2018-02-14 8:22</t>
+          <t>2018-02-14T8:22</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2018-02-14 11:18</t>
+          <t>2018-02-14T11:18</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D94">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2018-02-21 NA</t>
+          <t>2018-02-21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2018-02-21 NA</t>
+          <t>2018-02-21</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D95">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2018-02-28 9:12</t>
+          <t>2018-02-28T9:12</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2018-02-28 12:18</t>
+          <t>2018-02-28T12:18</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D96">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2018-03-07 9:29</t>
+          <t>2018-03-07T9:29</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2018-03-07 12:25</t>
+          <t>2018-03-07T12:25</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D97">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2018-03-14 9:31</t>
+          <t>2018-03-14T9:31</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2018-03-14 12:27</t>
+          <t>2018-03-14T12:27</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PEAR1409151109-01007</t>
+          <t>PEAR14091511-ESP09-01007</t>
         </is>
       </c>
       <c r="D98">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2018-03-21 9:58</t>
+          <t>2018-03-21T9:58</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2018-03-21 12:54</t>
+          <t>2018-03-21T12:54</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D99">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2018-01-11 9:19</t>
+          <t>2018-01-11T9:19</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2018-01-11 12:15</t>
+          <t>2018-01-11T12:15</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D100">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2018-01-18 9:11</t>
+          <t>2018-01-18T9:11</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2018-01-18 12:17</t>
+          <t>2018-01-18T12:17</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D101">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2018-01-25 9:17</t>
+          <t>2018-01-25T9:17</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2018-01-25 12:13</t>
+          <t>2018-01-25T12:13</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D102">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2018-02-01 9:17</t>
+          <t>2018-02-01T9:17</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2018-02-01 12:13</t>
+          <t>2018-02-01T12:13</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D103">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2018-02-08 9:59</t>
+          <t>2018-02-08T9:59</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2018-02-08 12:55</t>
+          <t>2018-02-08T12:55</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D104">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2018-02-15 9:41</t>
+          <t>2018-02-15T9:41</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2018-02-15 12:37</t>
+          <t>2018-02-15T12:37</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D105">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2018-02-22 9:29</t>
+          <t>2018-02-22T9:29</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2018-02-22 12:25</t>
+          <t>2018-02-22T12:25</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PEAR1409151106-01003</t>
+          <t>PEAR14091511-EST06-01003</t>
         </is>
       </c>
       <c r="D106">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2018-03-01 9:31</t>
+          <t>2018-03-01T9:31</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2018-03-01 12:27</t>
+          <t>2018-03-01T12:27</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D107">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2018-01-13 9:21</t>
+          <t>2018-01-13T9:21</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2018-01-13 12:17</t>
+          <t>2018-01-13T12:17</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D108">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2018-01-20 9:25</t>
+          <t>2018-01-20T9:25</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2018-01-20 12:21</t>
+          <t>2018-01-20T12:21</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D109">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2018-01-27 9:54</t>
+          <t>2018-01-27T9:54</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2018-01-27 12:50</t>
+          <t>2018-01-27T12:50</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D110">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2018-02-03 9:37</t>
+          <t>2018-02-03T9:37</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2018-02-03 12:33</t>
+          <t>2018-02-03T12:33</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D111">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2018-02-10 NA</t>
+          <t>2018-02-10</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2018-02-10 NA</t>
+          <t>2018-02-10</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D112">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2018-02-17 9:54</t>
+          <t>2018-02-17T9:54</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2018-02-17 12:50</t>
+          <t>2018-02-17T12:50</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D113">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2018-02-24 9:58</t>
+          <t>2018-02-24T9:58</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2018-02-24 12:54</t>
+          <t>2018-02-24T12:54</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PEAR1409151129-02005</t>
+          <t>PEAR14091511-FRA29-02005</t>
         </is>
       </c>
       <c r="D114">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2018-03-03 NA</t>
+          <t>2018-03-03</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2018-03-03 NA</t>
+          <t>2018-03-03</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D115">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2018-02-18 8:13</t>
+          <t>2018-02-18T8:13</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2018-02-18 11:19</t>
+          <t>2018-02-18T11:19</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D116">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2018-02-25 8:18</t>
+          <t>2018-02-25T8:18</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2018-02-25 11:14</t>
+          <t>2018-02-25T11:14</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D117">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2018-03-04 8:27</t>
+          <t>2018-03-04T8:27</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2018-03-04 11:23</t>
+          <t>2018-03-04T11:23</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D118">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2018-03-11 NA</t>
+          <t>2018-03-11</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2018-03-11 NA</t>
+          <t>2018-03-11</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D119">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2018-03-18 8:33</t>
+          <t>2018-03-18T8:33</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2018-03-18 11:29</t>
+          <t>2018-03-18T11:29</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D120">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2018-03-25 8:10</t>
+          <t>2018-03-25T8:10</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2018-03-25 11:16</t>
+          <t>2018-03-25T11:16</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D121">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2018-04-01 8:37</t>
+          <t>2018-04-01T8:37</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2018-04-01 11:33</t>
+          <t>2018-04-01T11:33</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PEAR1409151101-98974</t>
+          <t>PEAR14091511-ISR01-98974</t>
         </is>
       </c>
       <c r="D122">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2018-04-08 11:37</t>
+          <t>2018-04-08T11:37</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2018-04-08 14:33</t>
+          <t>2018-04-08T14:33</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PEAR1409151111-07851</t>
+          <t>PEAR14091511-ITL11-07851</t>
         </is>
       </c>
       <c r="D123">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2018-01-30 11:47</t>
+          <t>2018-01-30T11:47</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2018-01-30 14:43</t>
+          <t>2018-01-30T14:43</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PEAR1409151111-07851</t>
+          <t>PEAR14091511-ITL11-07851</t>
         </is>
       </c>
       <c r="D124">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2018-02-06 8:30</t>
+          <t>2018-02-06T8:30</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2018-02-06 11:26</t>
+          <t>2018-02-06T11:26</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PEAR1409151111-07851</t>
+          <t>PEAR14091511-ITL11-07851</t>
         </is>
       </c>
       <c r="D125">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2018-02-13 9:13</t>
+          <t>2018-02-13T9:13</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2018-02-13 12:16</t>
+          <t>2018-02-13T12:16</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D126">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2018-01-30 9:12</t>
+          <t>2018-01-30T9:12</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2018-01-30 12:18</t>
+          <t>2018-01-30T12:18</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D127">
@@ -6419,12 +6419,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2018-02-06 9:14</t>
+          <t>2018-02-06T9:14</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2018-02-06 12:10</t>
+          <t>2018-02-06T12:10</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D128">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2018-02-13 9:13</t>
+          <t>2018-02-13T9:13</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2018-02-13 12:19</t>
+          <t>2018-02-13T12:19</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D129">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2018-02-20 9:34</t>
+          <t>2018-02-20T9:34</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2018-02-20 12:30</t>
+          <t>2018-02-20T12:30</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D130">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2018-02-27 9:54</t>
+          <t>2018-02-27T9:54</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2018-02-27 12:50</t>
+          <t>2018-02-27T12:50</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D131">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2018-03-06 9:31</t>
+          <t>2018-03-06T9:31</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2018-03-06 12:27</t>
+          <t>2018-03-06T12:27</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PEAR1409151101-08081</t>
+          <t>PEAR14091511-KOR01-08081</t>
         </is>
       </c>
       <c r="D132">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2018-03-13 8:45</t>
+          <t>2018-03-13T8:45</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2018-03-13 11:41</t>
+          <t>2018-03-13T11:41</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PEAR1409151108-07044</t>
+          <t>PEAR14091511-NOR08-07044</t>
         </is>
       </c>
       <c r="D133">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2018-01-24 8:19</t>
+          <t>2018-01-24T8:19</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2018-01-24 11:15</t>
+          <t>2018-01-24T11:15</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PEAR1409151109-80891</t>
+          <t>PEAR14091511-POR09-80891</t>
         </is>
       </c>
       <c r="D134">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2018-01-21 8:58</t>
+          <t>2018-01-21T8:58</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2018-01-21 11:54</t>
+          <t>2018-01-21T11:54</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PEAR1409151109-80891</t>
+          <t>PEAR14091511-POR09-80891</t>
         </is>
       </c>
       <c r="D135">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2018-01-28 8:55</t>
+          <t>2018-01-28T8:55</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2018-01-28 11:51</t>
+          <t>2018-01-28T11:51</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PEAR1409151109-80891</t>
+          <t>PEAR14091511-POR09-80891</t>
         </is>
       </c>
       <c r="D136">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2018-02-04 8:37</t>
+          <t>2018-02-04T8:37</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2018-02-04 11:33</t>
+          <t>2018-02-04T11:33</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D137">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2018-02-14 8:23</t>
+          <t>2018-02-14T8:23</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2018-02-14 11:19</t>
+          <t>2018-02-14T11:19</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D138">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2018-02-21 8:37</t>
+          <t>2018-02-21T8:37</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2018-02-21 11:33</t>
+          <t>2018-02-21T11:33</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D139">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2018-02-28 8:53</t>
+          <t>2018-02-28T8:53</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2018-02-28 11:49</t>
+          <t>2018-02-28T11:49</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D140">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2018-03-07 8:53</t>
+          <t>2018-03-07T8:53</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2018-03-07 11:49</t>
+          <t>2018-03-07T11:49</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D141">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2018-03-14 10:45</t>
+          <t>2018-03-14T10:45</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2018-03-14 13:41</t>
+          <t>2018-03-14T13:41</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D142">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2018-03-21 10:30</t>
+          <t>2018-03-21T10:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2018-03-21 13:26</t>
+          <t>2018-03-21T13:26</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PEAR1409151111-11210</t>
+          <t>PEAR14091511-SLO11-11210</t>
         </is>
       </c>
       <c r="D143">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2018-03-28 10:43</t>
+          <t>2018-03-28T10:43</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2018-03-28 13:39</t>
+          <t>2018-03-28T13:39</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
